--- a/data/StormShadow.xlsx
+++ b/data/StormShadow.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N449"/>
+  <dimension ref="A1:N464"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="65.25" customWidth="1" style="16" min="1" max="1"/>
@@ -1334,7 +1334,6 @@
         </is>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="A129" s="8" t="inlineStr">
         <is>
@@ -9195,6 +9194,111 @@
       <c r="N449" s="15" t="inlineStr">
         <is>
           <t>wow_skincare_tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/skinnbydeepanshu/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kareenatekwani/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/freedom_chandel/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glowwithaashi_/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/khyati.3am/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glow_withsandy/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_anjali_skin_kochi/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sneha_skincare_vizag/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mysore_skin_lab/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tanvi_skin_nagpur/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_rutu_dermat_vadodara/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bhubaneswar_skincare_diaries/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/siliguri_skin_review/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/udaipur_dermat_care/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/himanshi_freshfacebeauty/reels/</t>
         </is>
       </c>
     </row>
@@ -9666,6 +9770,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A447" r:id="rId445"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A448" r:id="rId446"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A449" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A450" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A451" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A452" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A453" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A454" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A455" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A456" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A457" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A458" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A459" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A460" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A461" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A462" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A463" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A464" r:id="rId462"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/StormShadow.xlsx
+++ b/data/StormShadow.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N464"/>
+  <dimension ref="A1:N449"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="65.25" customWidth="1" style="16" min="1" max="1"/>
@@ -9194,111 +9194,6 @@
       <c r="N449" s="15" t="inlineStr">
         <is>
           <t>wow_skincare_tips</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/skinnbydeepanshu/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/kareenatekwani/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/freedom_chandel/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/glowwithaashi_/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/khyati.3am/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/glow_withsandy/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dr_anjali_skin_kochi/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/sneha_skincare_vizag/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/mysore_skin_lab/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/tanvi_skin_nagpur/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/dr_rutu_dermat_vadodara/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/bhubaneswar_skincare_diaries/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/siliguri_skin_review/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/udaipur_dermat_care/reels/</t>
-        </is>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/himanshi_freshfacebeauty/reels/</t>
         </is>
       </c>
     </row>
@@ -9770,21 +9665,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A447" r:id="rId445"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A448" r:id="rId446"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A449" r:id="rId447"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A450" r:id="rId448"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A451" r:id="rId449"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A452" r:id="rId450"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A453" r:id="rId451"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A454" r:id="rId452"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A455" r:id="rId453"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A456" r:id="rId454"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A457" r:id="rId455"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A458" r:id="rId456"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A459" r:id="rId457"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A460" r:id="rId458"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A461" r:id="rId459"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A462" r:id="rId460"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A463" r:id="rId461"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A464" r:id="rId462"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/StormShadow.xlsx
+++ b/data/StormShadow.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N449"/>
+  <dimension ref="A1:N453"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="65.25" customWidth="1" style="16" min="1" max="1"/>
@@ -9194,6 +9194,34 @@
       <c r="N449" s="15" t="inlineStr">
         <is>
           <t>wow_skincare_tips</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/skinnbydeepanshu/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glowwithaashi_/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tanishachawlaa/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/calmcarejourney/reels/</t>
         </is>
       </c>
     </row>
@@ -9665,6 +9693,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A447" r:id="rId445"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A448" r:id="rId446"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A449" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A450" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A451" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A452" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A453" r:id="rId451"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/StormShadow.xlsx
+++ b/data/StormShadow.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D314"/>
+  <dimension ref="A1:I326"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="65.25" customWidth="1" style="14" min="1" max="1"/>
@@ -2649,18 +2649,90 @@
         </is>
       </c>
     </row>
-    <row r="315" ht="15.75" customHeight="1" s="14"/>
-    <row r="316" ht="15.75" customHeight="1" s="14"/>
-    <row r="317" ht="15.75" customHeight="1" s="14"/>
-    <row r="318" ht="15.75" customHeight="1" s="14"/>
-    <row r="319" ht="15.75" customHeight="1" s="14"/>
-    <row r="320" ht="15.75" customHeight="1" s="14"/>
-    <row r="321" ht="15.75" customHeight="1" s="14"/>
-    <row r="322" ht="15.75" customHeight="1" s="14"/>
-    <row r="323" ht="15.75" customHeight="1" s="14"/>
-    <row r="324" ht="15.75" customHeight="1" s="14"/>
-    <row r="325" ht="15.75" customHeight="1" s="14"/>
-    <row r="326" ht="15.75" customHeight="1" s="14"/>
+    <row r="315" ht="15.75" customHeight="1" s="14">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/srisa_skincare/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="15.75" customHeight="1" s="14">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ugcbloomsisters/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="15.75" customHeight="1" s="14">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/paintedcharisma/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="15.75" customHeight="1" s="14">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glowwithugc.in/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="15.75" customHeight="1" s="14">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ugcwithkinjal/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="15.75" customHeight="1" s="14">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/prachii.kaul/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="15.75" customHeight="1" s="14">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/narayani_dogra/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="15.75" customHeight="1" s="14">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shitu_bhardwazzz/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="15.75" customHeight="1" s="14">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/heyy_bhargavi/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="15.75" customHeight="1" s="14">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ugcwithmantasha/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="15.75" customHeight="1" s="14">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shivaniiugc/reels/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="15.75" customHeight="1" s="14">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/khyati.3am/reels/</t>
+        </is>
+      </c>
+    </row>
     <row r="327" ht="15.75" customHeight="1" s="14"/>
     <row r="328" ht="15.75" customHeight="1" s="14"/>
     <row r="329" ht="15.75" customHeight="1" s="14"/>
@@ -3668,6 +3740,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A312" r:id="rId310"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A313" r:id="rId311"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A314" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A315" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A316" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A317" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A318" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A319" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A320" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A321" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A322" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A323" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A324" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A325" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A326" r:id="rId324"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/data/StormShadow.xlsx
+++ b/data/StormShadow.xlsx
@@ -2650,86 +2650,86 @@
       </c>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="14">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/srisa_skincare/reels/</t>
+      <c r="A315" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/skinnbydeepanshu/reels/</t>
         </is>
       </c>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="14">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/ugcbloomsisters/reels/</t>
+      <c r="A316" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kareenatekwani/reels/</t>
         </is>
       </c>
     </row>
     <row r="317" ht="15.75" customHeight="1" s="14">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/paintedcharisma/reels/</t>
+      <c r="A317" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glowwithaashi_/reels/</t>
         </is>
       </c>
     </row>
     <row r="318" ht="15.75" customHeight="1" s="14">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/glowwithugc.in/reels/</t>
+      <c r="A318" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/glow_withsandy/reels/</t>
         </is>
       </c>
     </row>
     <row r="319" ht="15.75" customHeight="1" s="14">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/ugcwithkinjal/reels/</t>
+      <c r="A319" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_anjali_skin_kochi/reels/</t>
         </is>
       </c>
     </row>
     <row r="320" ht="15.75" customHeight="1" s="14">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/prachii.kaul/reels/</t>
+      <c r="A320" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sneha_skincare_vizag/reels/</t>
         </is>
       </c>
     </row>
     <row r="321" ht="15.75" customHeight="1" s="14">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/narayani_dogra/reels/</t>
+      <c r="A321" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mysore_skin_lab/reels/</t>
         </is>
       </c>
     </row>
     <row r="322" ht="15.75" customHeight="1" s="14">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/shitu_bhardwazzz/reels/</t>
+      <c r="A322" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tanvi_skin_nagpur/reels/</t>
         </is>
       </c>
     </row>
     <row r="323" ht="15.75" customHeight="1" s="14">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/heyy_bhargavi/reels/</t>
+      <c r="A323" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dr_rutu_dermat_vadodara/reels/</t>
         </is>
       </c>
     </row>
     <row r="324" ht="15.75" customHeight="1" s="14">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/ugcwithmantasha/reels/</t>
+      <c r="A324" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bhubaneswar_skincare_diaries/reels/</t>
         </is>
       </c>
     </row>
     <row r="325" ht="15.75" customHeight="1" s="14">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/shivaniiugc/reels/</t>
+      <c r="A325" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/siliguri_skin_review/reels/</t>
         </is>
       </c>
     </row>
     <row r="326" ht="15.75" customHeight="1" s="14">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/khyati.3am/reels/</t>
+      <c r="A326" s="4" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/udaipur_dermat_care/reels/</t>
         </is>
       </c>
     </row>
